--- a/testing/reports/appiumtesting.xlsx
+++ b/testing/reports/appiumtesting.xlsx
@@ -669,7 +669,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 10:03:44   |   Suites: App launch · Login · Navigation · Upload E2E</t>
+          <t>Generated: 2026-07-23 09:12:21   |   Suites: App launch · Login · Navigation · Upload E2E</t>
         </is>
       </c>
     </row>
